--- a/output/pdf_financials_xlsx/CPL.xlsx
+++ b/output/pdf_financials_xlsx/CPL.xlsx
@@ -1205,28 +1205,28 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.6514219999999999</v>
+        <v>-0.6514219999999999</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.259308</v>
+        <v>-0.259308</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.974703</v>
+        <v>-0.974703</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.191924</v>
+        <v>-0.191924</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.909263</v>
+        <v>-2.909263</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.344957</v>
+        <v>-2.344957</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.684208</v>
+        <v>-1.684208</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.390061</v>
+        <v>-0.390061</v>
       </c>
     </row>
     <row r="17">
@@ -1465,28 +1465,28 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.6514219999999999</v>
+        <v>-0.6514219999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.259308</v>
+        <v>-0.259308</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.974703</v>
+        <v>-0.974703</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.191924</v>
+        <v>-0.191924</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.909263</v>
+        <v>-2.909263</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.344957</v>
+        <v>-2.344957</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.684208</v>
+        <v>-1.684208</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.390061</v>
+        <v>-0.390061</v>
       </c>
     </row>
     <row r="21">
@@ -1624,28 +1624,28 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.6514219999999999</v>
+        <v>-0.6514219999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.259308</v>
+        <v>-0.259308</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.974703</v>
+        <v>-0.974703</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.191924</v>
+        <v>-0.191924</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.909263</v>
+        <v>-2.909263</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.344957</v>
+        <v>-2.344957</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.684208</v>
+        <v>-1.684208</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.390061</v>
+        <v>-0.390061</v>
       </c>
     </row>
     <row r="24">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>54.285167</v>
+        <v>-54.285167</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>207.8045</v>
+        <v>-207.8045</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -1850,28 +1850,28 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.6514219999999999</v>
+        <v>-0.6514219999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.259308</v>
+        <v>-0.259308</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.974703</v>
+        <v>-0.974703</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.191924</v>
+        <v>-0.191924</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.909263</v>
+        <v>-2.909263</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.344957</v>
+        <v>-2.344957</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.684208</v>
+        <v>-1.684208</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.390061</v>
+        <v>-0.390061</v>
       </c>
     </row>
     <row r="28">
@@ -1956,28 +1956,28 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.6514219999999999</v>
+        <v>-0.6514219999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.259308</v>
+        <v>-0.259308</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.974703</v>
+        <v>-0.974703</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.191924</v>
+        <v>-0.191924</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.909263</v>
+        <v>-2.909263</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.344957</v>
+        <v>-2.344957</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.684208</v>
+        <v>-1.684208</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.390061</v>
+        <v>-0.390061</v>
       </c>
     </row>
     <row r="30">
@@ -2086,28 +2086,28 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5255,43 +5255,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.272094</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.526938</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.774887</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.79195</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.79195</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.135411</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.289535</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.281854</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.445908</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.351542</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.377538</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.39473</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.540239</v>
       </c>
       <c r="O92" s="1" t="inlineStr">
         <is>
@@ -6596,10 +6596,10 @@
         <v>-0.875926</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.741653</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.07549</v>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>0</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="119">
@@ -8676,7 +8676,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -9834,7 +9838,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -10432,7 +10440,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -11612,7 +11624,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>0.272094</v>
       </c>
@@ -12618,7 +12634,11 @@
           <t>Share-based payments for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -17092,7 +17112,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -19628,28 +19652,28 @@
         </is>
       </c>
       <c r="K144" s="5" t="n">
-        <v>0.6514219999999999</v>
+        <v>-0.6514219999999999</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>0.259308</v>
+        <v>-0.259308</v>
       </c>
       <c r="M144" s="5" t="n">
-        <v>0.974703</v>
+        <v>-0.974703</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>0.191924</v>
+        <v>-0.191924</v>
       </c>
       <c r="O144" s="5" t="n">
-        <v>2.909263</v>
+        <v>-2.909263</v>
       </c>
       <c r="P144" s="5" t="n">
-        <v>2.344957</v>
+        <v>-2.344957</v>
       </c>
       <c r="Q144" s="5" t="n">
-        <v>1.684208</v>
+        <v>-1.684208</v>
       </c>
       <c r="R144" s="5" t="n">
-        <v>0.390061</v>
+        <v>-0.390061</v>
       </c>
     </row>
     <row r="145">

--- a/output/pdf_financials_xlsx/CPL.xlsx
+++ b/output/pdf_financials_xlsx/CPL.xlsx
@@ -899,16 +899,16 @@
         <v>0.09393799999999999</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.252553</v>
+        <v>2.941505</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.437935</v>
+        <v>2.495833</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.435893</v>
+        <v>1.778408</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.235892</v>
+        <v>0.390061</v>
       </c>
     </row>
     <row r="11">
@@ -952,16 +952,16 @@
         <v>-0.09393799999999999</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.252553</v>
+        <v>-2.941505</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.437935</v>
+        <v>-2.495833</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.435893</v>
+        <v>-1.778408</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.235892</v>
+        <v>-0.390061</v>
       </c>
     </row>
     <row r="12">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00045</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003705</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002944</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000122</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1769,15 +1769,13 @@
         <v>15.469133</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>24.78052</v>
+        <v>25.063044</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>37.45705</v>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>37.866282</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>38.266282</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1833,16 +1831,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.392222</v>
+        <v>-1.392672</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.239026</v>
+        <v>-1.242731</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.7491409999999999</v>
+        <v>-0.752085</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.023232</v>
+        <v>0.02311</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1939,16 +1937,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.392222</v>
+        <v>-1.392672</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.239026</v>
+        <v>-1.242731</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.7491409999999999</v>
+        <v>-0.752085</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.023232</v>
+        <v>0.02311</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2231,13 +2229,13 @@
         <v>0.041396</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.668333</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.084275</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.003724</v>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
@@ -2333,13 +2331,13 @@
         <v>0.041396</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.668333</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.084275</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.003724</v>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
@@ -2945,13 +2943,13 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.746713</v>
+        <v>0.07838000000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.096</v>
+        <v>0.011725</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.025276</v>
+        <v>0.021552</v>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
@@ -7686,7 +7684,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -19452,7 +19450,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27956,7 +27954,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -28306,7 +28304,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -30526,7 +30524,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -30868,7 +30866,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">

--- a/output/pdf_financials_xlsx/CPL.xlsx
+++ b/output/pdf_financials_xlsx/CPL.xlsx
@@ -2237,10 +2237,8 @@
       <c r="N34" s="3" t="n">
         <v>0.003724</v>
       </c>
-      <c r="O34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>0.001186</v>
       </c>
     </row>
     <row r="35">
@@ -2288,10 +2286,8 @@
       <c r="N35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2339,10 +2335,8 @@
       <c r="N36" s="3" t="n">
         <v>0.003724</v>
       </c>
-      <c r="O36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>0.001186</v>
       </c>
     </row>
     <row r="37">
@@ -2390,10 +2384,8 @@
       <c r="N37" s="3" t="n">
         <v>0.004238</v>
       </c>
-      <c r="O37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2441,10 +2433,8 @@
       <c r="N38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2492,10 +2482,8 @@
       <c r="N39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2543,10 +2531,8 @@
       <c r="N40" s="3" t="n">
         <v>0.025905</v>
       </c>
-      <c r="O40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>0.005741</v>
       </c>
     </row>
     <row r="41">
@@ -2594,10 +2580,8 @@
       <c r="N41" s="3" t="n">
         <v>0.030143</v>
       </c>
-      <c r="O41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>0.005741</v>
       </c>
     </row>
     <row r="42">
@@ -2645,10 +2629,8 @@
       <c r="N42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2696,10 +2678,8 @@
       <c r="N43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2747,10 +2727,8 @@
       <c r="N44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2798,10 +2776,8 @@
       <c r="N45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2849,10 +2825,8 @@
       <c r="N46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2900,10 +2874,8 @@
       <c r="N47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2951,10 +2923,8 @@
       <c r="N48" s="3" t="n">
         <v>0.021552</v>
       </c>
-      <c r="O48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>0.008920000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3002,10 +2972,8 @@
       <c r="N49" s="3" t="n">
         <v>0.055419</v>
       </c>
-      <c r="O49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>0.015847</v>
       </c>
     </row>
     <row r="50">
@@ -3053,10 +3021,8 @@
       <c r="N50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3104,10 +3070,8 @@
       <c r="N51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3155,10 +3119,8 @@
       <c r="N52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3206,10 +3168,8 @@
       <c r="N53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3257,10 +3217,8 @@
       <c r="N54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3385,10 +3343,8 @@
       <c r="N56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3436,10 +3392,8 @@
       <c r="N57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3487,10 +3441,8 @@
       <c r="N58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3538,10 +3490,8 @@
       <c r="N59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3589,10 +3539,8 @@
       <c r="N60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3640,10 +3588,8 @@
       <c r="N61" s="3" t="n">
         <v>2.548862</v>
       </c>
-      <c r="O61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>2.548862</v>
       </c>
     </row>
     <row r="62">
@@ -3701,10 +3647,8 @@
       <c r="N62" s="3" t="n">
         <v>2.548862</v>
       </c>
-      <c r="O62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O62" s="3" t="n">
+        <v>2.548862</v>
       </c>
     </row>
     <row r="63">
@@ -3762,10 +3706,8 @@
       <c r="N63" s="3" t="n">
         <v>2.604281</v>
       </c>
-      <c r="O63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>2.564709</v>
       </c>
     </row>
     <row r="64">
@@ -3813,10 +3755,8 @@
       <c r="N64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3864,10 +3804,8 @@
       <c r="N65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3915,10 +3853,8 @@
       <c r="N66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3966,10 +3902,8 @@
       <c r="N67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4017,10 +3951,8 @@
       <c r="N68" s="3" t="n">
         <v>1.438773</v>
       </c>
-      <c r="O68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O68" s="3" t="n">
+        <v>1.684516</v>
       </c>
     </row>
     <row r="69">
@@ -4068,10 +4000,8 @@
       <c r="N69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4119,10 +4049,8 @@
       <c r="N70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4170,10 +4098,8 @@
       <c r="N71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4221,10 +4147,8 @@
       <c r="N72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4272,10 +4196,8 @@
       <c r="N73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4323,10 +4245,8 @@
       <c r="N74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4374,10 +4294,8 @@
       <c r="N75" s="3" t="n">
         <v>0.050043</v>
       </c>
-      <c r="O75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4486,10 +4404,8 @@
       <c r="N77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4537,10 +4453,8 @@
       <c r="N78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4588,10 +4502,8 @@
       <c r="N79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4710,10 +4622,8 @@
       <c r="N81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4761,10 +4671,8 @@
       <c r="N82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -4812,10 +4720,8 @@
       <c r="N83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -4863,10 +4769,8 @@
       <c r="N84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -4914,10 +4818,8 @@
       <c r="N85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5036,10 +4938,8 @@
       <c r="N87" s="3" t="n">
         <v>1.488816</v>
       </c>
-      <c r="O87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O87" s="3" t="n">
+        <v>1.834305</v>
       </c>
     </row>
     <row r="88">
@@ -5087,10 +4987,8 @@
       <c r="N88" s="3" t="n">
         <v>22.13215</v>
       </c>
-      <c r="O88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O88" s="3" t="n">
+        <v>22.13715</v>
       </c>
     </row>
     <row r="89">
@@ -5138,10 +5036,8 @@
       <c r="N89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5189,10 +5085,8 @@
       <c r="N90" s="3" t="n">
         <v>-22.556924</v>
       </c>
-      <c r="O90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O90" s="3" t="n">
+        <v>-22.676272</v>
       </c>
     </row>
     <row r="91">
@@ -5240,10 +5134,8 @@
       <c r="N91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5291,10 +5183,8 @@
       <c r="N92" s="3" t="n">
         <v>1.540239</v>
       </c>
-      <c r="O92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O92" s="3" t="n">
+        <v>1.269526</v>
       </c>
     </row>
     <row r="93">
@@ -5342,10 +5232,8 @@
       <c r="N93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5393,10 +5281,8 @@
       <c r="N94" s="3" t="n">
         <v>1.115465</v>
       </c>
-      <c r="O94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O94" s="3" t="n">
+        <v>0.7304040000000001</v>
       </c>
     </row>
     <row r="95">
@@ -5444,10 +5330,8 @@
       <c r="N95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5495,10 +5379,8 @@
       <c r="N96" s="3" t="n">
         <v>1.115465</v>
       </c>
-      <c r="O96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O96" s="3" t="n">
+        <v>0.7304040000000001</v>
       </c>
     </row>
     <row r="97">
@@ -5556,10 +5438,8 @@
       <c r="N97" s="3" t="n">
         <v>0.4283197550494743</v>
       </c>
-      <c r="O97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O97" s="3" t="n">
+        <v>0.2847902042687884</v>
       </c>
     </row>
     <row r="98">
@@ -5704,28 +5584,28 @@
         </is>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.021488</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.024346</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002521</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000683</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009391999999999999</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>-0.005591</v>
+        <v>0.015644</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0.001353</v>
+        <v>0.008473</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0.004238</v>
+        <v>0.024402</v>
       </c>
     </row>
     <row r="102">
@@ -5969,28 +5849,28 @@
         </is>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.046409</v>
+        <v>-0.067897</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.054288</v>
+        <v>0.078634</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.046988</v>
+        <v>-0.049509</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.107526</v>
+        <v>0.106843</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.130124</v>
+        <v>0.120732</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.453543</v>
+        <v>0.474778</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.916644</v>
+        <v>0.923764</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.262613</v>
+        <v>0.282777</v>
       </c>
     </row>
     <row r="107">
@@ -7746,10 +7626,8 @@
       <c r="Q2" s="5" t="n">
         <v>0.003724</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R2" s="5" t="n">
+        <v>0.001186</v>
       </c>
     </row>
     <row r="3">
@@ -7910,10 +7788,8 @@
       <c r="Q4" s="5" t="n">
         <v>0.025905</v>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R4" s="5" t="n">
+        <v>0.005741</v>
       </c>
     </row>
     <row r="5">
@@ -7996,10 +7872,8 @@
       <c r="Q5" s="5" t="n">
         <v>0.021552</v>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R5" s="5" t="n">
+        <v>0.008920000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -8082,10 +7956,8 @@
       <c r="Q6" s="5" t="n">
         <v>0.055419</v>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R6" s="5" t="n">
+        <v>0.015847</v>
       </c>
     </row>
     <row r="7">
@@ -8158,10 +8030,8 @@
       <c r="Q7" s="5" t="n">
         <v>2.548862</v>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R7" s="5" t="n">
+        <v>2.548862</v>
       </c>
     </row>
     <row r="8">
@@ -8234,10 +8104,8 @@
       <c r="Q8" s="5" t="n">
         <v>2.604281</v>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R8" s="5" t="n">
+        <v>2.564709</v>
       </c>
     </row>
     <row r="9">
@@ -8320,10 +8188,8 @@
       <c r="Q9" s="5" t="n">
         <v>1.438773</v>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R9" s="5" t="n">
+        <v>1.684516</v>
       </c>
     </row>
     <row r="10">
@@ -8404,10 +8270,8 @@
       <c r="Q10" s="5" t="n">
         <v>0.050043</v>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R10" s="5" t="n">
+        <v>0.149789</v>
       </c>
     </row>
     <row r="11">
@@ -8423,12 +8287,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Current liabilities total</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -8456,30 +8320,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J11" s="5" t="n">
+        <v>0.802792</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.700256</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0.395962</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0.363052</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0.510013</v>
       </c>
       <c r="O11" s="5" t="n">
         <v>0.244734</v>
@@ -8490,10 +8344,8 @@
       <c r="Q11" s="5" t="n">
         <v>1.488816</v>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R11" s="5" t="n">
+        <v>1.834305</v>
       </c>
     </row>
     <row r="12">
@@ -8504,17 +8356,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Capital stock (note 5)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8542,34 +8394,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0.802792</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0.700256</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0.395962</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0.363052</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0.510013</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O12" s="5" t="n">
-        <v>0.244734</v>
+        <v>20.403076</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.6086549999999999</v>
+        <v>21.557089</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>1.488816</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>22.13215</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>22.13715</v>
       </c>
     </row>
     <row r="13">
@@ -8585,12 +8445,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Capital stock (note 5)</t>
+          <t>Reserves (note 5)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8644,18 +8504,16 @@
         </is>
       </c>
       <c r="O13" s="5" t="n">
-        <v>20.403076</v>
+        <v>1.377538</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>21.557089</v>
+        <v>1.39473</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>22.13215</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.540239</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>1.269526</v>
       </c>
     </row>
     <row r="14">
@@ -8671,12 +8529,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reserves (note 5)</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -8714,34 +8572,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L14" s="5" t="n">
+        <v>-13.125587</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>-14.10029</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>-14.185671</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>1.377538</v>
+        <v>-18.675513</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>1.39473</v>
+        <v>-20.876996</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>1.540239</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-22.556924</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>-22.676272</v>
       </c>
     </row>
     <row r="15">
@@ -8757,12 +8607,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Total shareholders’ equity</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -8801,27 +8651,25 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>-13.125587</v>
+        <v>2.303401</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>-14.10029</v>
+        <v>2.267057</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>-14.185671</v>
+        <v>2.150528</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>-18.675513</v>
+        <v>3.105101</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-20.876996</v>
+        <v>2.074823</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>-22.556924</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.115465</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0.7304040000000001</v>
       </c>
     </row>
     <row r="16">
@@ -8837,12 +8685,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity</t>
+          <t>Total liabilities and shareholders’ equity $</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -8881,27 +8729,25 @@
         </is>
       </c>
       <c r="L16" s="5" t="n">
-        <v>2.303401</v>
+        <v>2.699363</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>2.267057</v>
+        <v>2.630109</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>2.150528</v>
+        <v>2.660541</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3.105101</v>
+        <v>3.349835</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>2.074823</v>
+        <v>2.683478</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>1.115465</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.604281</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>2.564709</v>
       </c>
     </row>
     <row r="17">
@@ -8912,17 +8758,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Total liabilities and shareholders’ equity $</t>
+          <t>Current liabilities total</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8960,23 +8806,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n">
-        <v>2.699363</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>2.630109</v>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>2.660541</v>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O17" s="5" t="n">
-        <v>3.349835</v>
+        <v>0.244734</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>2.683478</v>
+        <v>0.6086549999999999</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>2.604281</v>
+        <v>1.488816</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -12890,7 +12742,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
